--- a/scraped_codes.xlsx
+++ b/scraped_codes.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Link</t>
   </si>
@@ -22,10 +22,34 @@
     <t>Product Code_scraped</t>
   </si>
   <si>
-    <t>https://www.skyquestt.com/report/digital-bss-market</t>
-  </si>
-  <si>
-    <t>SQMIG45I2276</t>
+    <t>https://www.skyquestt.com/report/pet-accessories-market</t>
+  </si>
+  <si>
+    <t>https://www.skyquestt.com/report/digital-health-market</t>
+  </si>
+  <si>
+    <t>https://www.skyquestt.com/report/growth-hormone-deficiency-market</t>
+  </si>
+  <si>
+    <t>https://www.skyquestt.com/report/power-tools-market</t>
+  </si>
+  <si>
+    <t>https://www.skyquestt.com/report/corneal-transplant-market</t>
+  </si>
+  <si>
+    <t>SQMIG35E2047</t>
+  </si>
+  <si>
+    <t>SQMIG35G2310</t>
+  </si>
+  <si>
+    <t>SQMIG35A2816</t>
+  </si>
+  <si>
+    <t>SQMIG20D2077</t>
+  </si>
+  <si>
+    <t>SQMIG35A2814</t>
   </si>
 </sst>
 </file>
@@ -396,7 +420,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -412,12 +436,48 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="2" t="s">
         <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1"/>
+    <hyperlink ref="A3" r:id="rId2"/>
+    <hyperlink ref="A4" r:id="rId3"/>
+    <hyperlink ref="A5" r:id="rId4"/>
+    <hyperlink ref="A6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
